--- a/data/trans_camb/P1002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,1</t>
+          <t>-1,76; 1,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,6</t>
+          <t>-1,58; 2,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,95</t>
+          <t>-2,46; 2,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,24</t>
+          <t>-0,81; 4,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,63</t>
+          <t>-2,72; 1,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 8,2</t>
+          <t>-0,64; 7,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,53</t>
+          <t>-0,65; 2,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,32</t>
+          <t>-1,42; 1,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,4</t>
+          <t>-1,06; 3,03</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,05; 261,49</t>
+          <t>-64,43; 253,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 295,78</t>
+          <t>-65,18; 299,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 692,36</t>
+          <t>-100,0; 398,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 238,81</t>
+          <t>-25,6; 203,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,64; 97,72</t>
+          <t>-71,71; 93,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 418,9</t>
+          <t>-29,56; 359,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 166,52</t>
+          <t>-22,52; 158,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 82,49</t>
+          <t>-47,88; 95,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,46; 202,25</t>
+          <t>-44,85; 184,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,1</t>
+          <t>-1,7; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,33</t>
+          <t>-0,89; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,47</t>
+          <t>-1,85; 3,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,71</t>
+          <t>-3,82; 1,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,34</t>
+          <t>-4,66; 0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,5</t>
+          <t>-4,12; 2,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,13</t>
+          <t>-1,93; 1,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,23</t>
+          <t>-1,95; 1,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,6</t>
+          <t>-1,8; 2,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 118,07</t>
+          <t>-49,53; 109,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 198,01</t>
+          <t>-29,55; 162,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 212,96</t>
+          <t>-61,54; 202,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 44,81</t>
+          <t>-50,31; 39,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 9,2</t>
+          <t>-64,13; 10,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,73; 53,36</t>
+          <t>-57,15; 47,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 33,87</t>
+          <t>-38,43; 36,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 36,46</t>
+          <t>-38,25; 41,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 73,27</t>
+          <t>-37,53; 62,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,93</t>
+          <t>-2,03; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,45</t>
+          <t>-3,13; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,91</t>
+          <t>-1,32; 4,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,27</t>
+          <t>2,95; 8,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,21</t>
+          <t>-1,63; 3,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,62</t>
+          <t>-2,11; 2,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,1</t>
+          <t>1,51; 5,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,66</t>
+          <t>-1,61; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,4</t>
+          <t>-0,93; 2,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 102,84</t>
+          <t>-38,7; 96,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 51,41</t>
+          <t>-56,93; 55,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 131,52</t>
+          <t>-25,18; 142,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,7; 217,39</t>
+          <t>41,97; 222,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 76,35</t>
+          <t>-26,61; 76,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 73,04</t>
+          <t>-32,86; 56,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,77; 127,71</t>
+          <t>25,16; 139,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 42,53</t>
+          <t>-30,01; 43,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 64,37</t>
+          <t>-17,46; 72,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,91</t>
+          <t>-0,99; 5,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,77</t>
+          <t>-0,97; 4,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,98</t>
+          <t>-3,67; 3,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 6,98</t>
+          <t>-0,61; 7,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,08</t>
+          <t>-3,49; 3,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 2,6</t>
+          <t>-4,86; 2,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,98</t>
+          <t>0,08; 4,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,05</t>
+          <t>-1,42; 3,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,55</t>
+          <t>-4,08; 1,7</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 156,1</t>
+          <t>-18,22; 155,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 145,62</t>
+          <t>-17,78; 136,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 80,41</t>
+          <t>-61,53; 87,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 89,78</t>
+          <t>-5,51; 100,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 42,06</t>
+          <t>-29,8; 46,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 32,48</t>
+          <t>-39,69; 29,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 80,47</t>
+          <t>-0,24; 84,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 50,64</t>
+          <t>-17,1; 50,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 23,12</t>
+          <t>-48,02; 25,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,31</t>
+          <t>-2,38; 5,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,44</t>
+          <t>-5,19; 1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,54</t>
+          <t>-3,16; 3,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,09</t>
+          <t>4,98; 14,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 10,79</t>
+          <t>1,72; 10,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,94</t>
+          <t>-1,08; 6,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,07</t>
+          <t>2,78; 9,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,43</t>
+          <t>-0,54; 4,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,64</t>
+          <t>-0,96; 3,87</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 94,66</t>
+          <t>-28,26; 91,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,82; 28,87</t>
+          <t>-55,3; 34,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 60,52</t>
+          <t>-33,48; 59,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40,96; 191,31</t>
+          <t>39,47; 187,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,34; 137,11</t>
+          <t>14,91; 142,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 78,94</t>
+          <t>-9,42; 80,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,38; 124,26</t>
+          <t>27,63; 125,86</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 74,21</t>
+          <t>-5,55; 67,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 50,84</t>
+          <t>-9,67; 54,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,58</t>
+          <t>-2,8; 7,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,1</t>
+          <t>-6,34; 2,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 1,19</t>
+          <t>-7,45; 0,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,54</t>
+          <t>1,63; 13,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,07</t>
+          <t>-2,05; 8,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 1,06</t>
+          <t>-12,41; 1,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,56</t>
+          <t>1,0; 8,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,7</t>
+          <t>-2,44; 5,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -0,25</t>
+          <t>-9,58; -0,47</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 88,15</t>
+          <t>-22,41; 96,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 41,56</t>
+          <t>-48,94; 33,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 17,88</t>
+          <t>-54,11; 13,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,78; 106,23</t>
+          <t>6,92; 103,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 76,14</t>
+          <t>-11,62; 76,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 10,2</t>
+          <t>-74,13; 9,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,29; 78,27</t>
+          <t>7,04; 78,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 43,23</t>
+          <t>-18,09; 44,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-64,58; -3,46</t>
+          <t>-67,67; -4,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 13,49</t>
+          <t>-2,19; 12,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 1,71</t>
+          <t>-10,47; 1,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 0,38</t>
+          <t>-11,54; -0,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,25; 20,48</t>
+          <t>6,73; 20,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 13,46</t>
+          <t>-0,03; 13,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 11,45</t>
+          <t>0,75; 11,59</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,34; 15,36</t>
+          <t>5,59; 15,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,93</t>
+          <t>-2,77; 6,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 5,71</t>
+          <t>-2,88; 5,28</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 108,23</t>
+          <t>-12,36; 106,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 13,63</t>
+          <t>-52,13; 14,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 3,07</t>
+          <t>-56,78; 0,4</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32,5; 133,77</t>
+          <t>30,11; 130,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 91,37</t>
+          <t>-0,81; 90,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,13; 78,59</t>
+          <t>3,52; 80,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,7; 102,78</t>
+          <t>26,25; 99,78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 45,81</t>
+          <t>-14,19; 42,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 39,08</t>
+          <t>-14,19; 37,14</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,86</t>
+          <t>0,39; 2,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,29</t>
+          <t>-0,9; 1,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,46</t>
+          <t>-1,23; 1,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,06</t>
+          <t>4,07; 7,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,63</t>
+          <t>0,83; 3,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,84</t>
+          <t>-0,57; 2,98</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,54</t>
+          <t>2,57; 4,57</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,06</t>
+          <t>0,27; 2,1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,87</t>
+          <t>-0,3; 1,93</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,52; 61,43</t>
+          <t>7,03; 59,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 28,6</t>
+          <t>-16,25; 26,26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 30,5</t>
+          <t>-21,92; 30,37</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44,25; 89,79</t>
+          <t>44,12; 91,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,2; 45,48</t>
+          <t>9,56; 46,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 35,68</t>
+          <t>-6,1; 37,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,21; 71,56</t>
+          <t>35,0; 71,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>3,46; 31,8</t>
+          <t>3,55; 32,82</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 28,85</t>
+          <t>-3,94; 29,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>1,13</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,99</t>
+          <t>-1,34; 2,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,37</t>
+          <t>-1,45; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,28</t>
+          <t>-2,36; 2,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,3</t>
+          <t>-0,78; 4,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,55</t>
+          <t>-2,9; 1,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,84</t>
+          <t>-0,37; 8,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,53</t>
+          <t>-0,7; 2,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,49</t>
+          <t>-1,56; 1,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,03</t>
+          <t>-0,91; 3,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-50,27%</t>
+          <t>-32,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106,89%</t>
+          <t>107,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 253,8</t>
+          <t>-60,92; 281,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 299,41</t>
+          <t>-62,05; 288,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 398,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 203,42</t>
+          <t>-21,88; 248,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,71; 93,42</t>
+          <t>-69,89; 93,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 359,66</t>
+          <t>-17,67; 395,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 158,75</t>
+          <t>-23,68; 151,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 95,43</t>
+          <t>-53,66; 76,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 184,08</t>
+          <t>-33,62; 201,11</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,87</t>
+          <t>-1,68; 1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,11</t>
+          <t>-0,72; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,61</t>
+          <t>-1,82; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,58</t>
+          <t>-3,62; 1,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 0,36</t>
+          <t>-4,64; 0,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,32</t>
+          <t>-3,03; 3,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,17</t>
+          <t>-1,99; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,33</t>
+          <t>-1,83; 1,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,3</t>
+          <t>-1,56; 2,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,87%</t>
+          <t>-3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 109,75</t>
+          <t>-48,74; 111,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 162,9</t>
+          <t>-25,94; 172,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,54; 202,06</t>
+          <t>-58,43; 182,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 39,17</t>
+          <t>-48,66; 40,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 10,38</t>
+          <t>-61,36; 12,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,15; 47,26</t>
+          <t>-43,8; 71,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 36,23</t>
+          <t>-40,37; 34,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 41,15</t>
+          <t>-38,0; 42,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 62,67</t>
+          <t>-33,73; 71,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,63</t>
+          <t>-1,93; 2,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,43</t>
+          <t>-2,88; 1,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,13</t>
+          <t>-1,56; 3,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,95</t>
+          <t>2,9; 8,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,07</t>
+          <t>-1,87; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,27</t>
+          <t>-2,22; 2,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,27</t>
+          <t>1,33; 5,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,61</t>
+          <t>-1,65; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,74</t>
+          <t>-1,29; 2,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 96,92</t>
+          <t>-36,36; 92,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,93; 55,06</t>
+          <t>-54,83; 55,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 142,96</t>
+          <t>-32,1; 118,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41,97; 222,07</t>
+          <t>44,5; 221,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 76,62</t>
+          <t>-29,41; 71,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 56,66</t>
+          <t>-33,6; 61,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,16; 139,61</t>
+          <t>22,65; 135,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 43,17</t>
+          <t>-30,17; 41,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 72,09</t>
+          <t>-23,09; 52,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,08</t>
+          <t>-1,02; 4,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,43</t>
+          <t>-1,35; 4,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,21</t>
+          <t>-1,12; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,45</t>
+          <t>-0,73; 7,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,72</t>
+          <t>-3,58; 3,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,26</t>
+          <t>-4,83; 1,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,98</t>
+          <t>0,12; 5,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,03</t>
+          <t>-1,26; 3,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,7</t>
+          <t>-2,04; 2,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,66%</t>
+          <t>-14,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,96%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 155,57</t>
+          <t>-18,78; 154,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 136,15</t>
+          <t>-22,67; 135,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 87,11</t>
+          <t>-22,67; 117,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 100,5</t>
+          <t>-6,79; 93,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 46,75</t>
+          <t>-31,29; 45,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 29,95</t>
+          <t>-39,35; 17,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 84,19</t>
+          <t>1,34; 83,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 50,24</t>
+          <t>-15,55; 51,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 25,54</t>
+          <t>-24,47; 34,8</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,41</t>
+          <t>-1,89; 5,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,84</t>
+          <t>-5,42; 1,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,3</t>
+          <t>-3,51; 3,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 14,5</t>
+          <t>4,82; 15,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,69</t>
+          <t>1,28; 10,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,05</t>
+          <t>-0,45; 6,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,03</t>
+          <t>2,68; 9,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,93</t>
+          <t>-0,57; 5,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,87</t>
+          <t>-1,04; 3,75</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>-1,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 91,27</t>
+          <t>-20,25; 100,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,3; 34,36</t>
+          <t>-58,02; 28,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 59,25</t>
+          <t>-39,04; 55,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39,47; 187,71</t>
+          <t>39,91; 197,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,91; 142,79</t>
+          <t>10,27; 130,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 80,27</t>
+          <t>-4,04; 90,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,63; 125,86</t>
+          <t>24,49; 119,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 67,76</t>
+          <t>-6,21; 68,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 54,32</t>
+          <t>-10,59; 50,92</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,99</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-1,38</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,94</t>
+          <t>-3,13; 7,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 2,61</t>
+          <t>-6,17; 2,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 0,95</t>
+          <t>-7,24; 0,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,01</t>
+          <t>1,07; 12,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 8,97</t>
+          <t>-1,64; 8,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 1,11</t>
+          <t>-4,28; 4,74</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,58</t>
+          <t>1,17; 8,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 5,03</t>
+          <t>-2,25; 4,57</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -0,47</t>
+          <t>-4,19; 1,66</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-27,34%</t>
+          <t>-28,4%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-35,12%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,01%</t>
+          <t>-11,06%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 96,93</t>
+          <t>-24,17; 88,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-48,94; 33,51</t>
+          <t>-49,54; 34,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 13,5</t>
+          <t>-53,63; 12,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,92; 103,4</t>
+          <t>6,46; 108,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 76,22</t>
+          <t>-10,56; 73,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,13; 9,59</t>
+          <t>-24,31; 42,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,04; 78,95</t>
+          <t>8,34; 79,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 44,78</t>
+          <t>-16,26; 41,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-67,67; -4,13</t>
+          <t>-28,91; 16,61</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-4,67</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,83</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>2,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 12,76</t>
+          <t>-1,2; 14,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 1,71</t>
+          <t>-11,03; 1,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,54; -0,11</t>
+          <t>-10,97; 0,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,73; 20,18</t>
+          <t>6,69; 20,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 13,42</t>
+          <t>-0,17; 12,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,75; 11,59</t>
+          <t>1,06; 12,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,59; 15,62</t>
+          <t>5,5; 15,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,59</t>
+          <t>-2,22; 7,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 5,28</t>
+          <t>-1,61; 6,64</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-32,58%</t>
+          <t>-29,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 106,99</t>
+          <t>-6,83; 111,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 14,15</t>
+          <t>-55,71; 12,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,78; 0,4</t>
+          <t>-53,02; 2,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30,11; 130,87</t>
+          <t>31,62; 136,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 90,02</t>
+          <t>-1,12; 83,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,52; 80,92</t>
+          <t>5,3; 82,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,25; 99,78</t>
+          <t>27,07; 99,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 42,93</t>
+          <t>-12,11; 48,64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 37,14</t>
+          <t>-8,12; 44,7</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,73</t>
+          <t>0,36; 2,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,22</t>
+          <t>-0,92; 1,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,43</t>
+          <t>-0,63; 1,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,18</t>
+          <t>3,87; 6,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,68</t>
+          <t>0,63; 3,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,98</t>
+          <t>1,04; 3,46</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,57</t>
+          <t>2,59; 4,51</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,1</t>
+          <t>0,3; 2,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,93</t>
+          <t>0,56; 2,31</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,03; 59,19</t>
+          <t>6,09; 58,56</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 26,26</t>
+          <t>-16,37; 26,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 30,37</t>
+          <t>-10,56; 36,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44,12; 91,04</t>
+          <t>40,8; 87,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,56; 46,76</t>
+          <t>6,9; 47,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 37,33</t>
+          <t>11,53; 44,8</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,0; 71,26</t>
+          <t>35,23; 70,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>3,55; 32,82</t>
+          <t>4,04; 32,98</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 29,72</t>
+          <t>7,7; 36,07</t>
         </is>
       </c>
     </row>
